--- a/data/trans_orig/Q5409A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36705</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>59636</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>59636</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>59636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60159</t>
+          <t>64892</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>87142</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>77577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90802</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>38009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104171</t>
+          <t>114830</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>104171</t>
+          <t>114830</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104171</t>
+          <t>114830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>158811</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>158811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>158811</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77759</t>
+          <t>84622</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>75774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86273</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>121580</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101977</t>
+          <t>110388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>133015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>41706</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>56238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
